--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.62299250158948</v>
+        <v>11.63873628150829</v>
       </c>
       <c r="D2" t="n">
-        <v>71.8918959735061</v>
+        <v>11.68243309569474</v>
       </c>
       <c r="E2" t="n">
-        <v>8.410500381452998</v>
+        <v>1.366706311986112</v>
       </c>
       <c r="F2" t="n">
-        <v>9.574595481210123</v>
+        <v>1.555871765696645</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.94030129392252</v>
+        <v>11.36529896026241</v>
       </c>
       <c r="D3" t="n">
-        <v>70.23701981701997</v>
+        <v>11.41351572026575</v>
       </c>
       <c r="E3" t="n">
-        <v>8.410500381452998</v>
+        <v>1.366706311986112</v>
       </c>
       <c r="F3" t="n">
-        <v>9.574595481210123</v>
+        <v>1.555871765696645</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.99989395481967</v>
+        <v>8.612482767658197</v>
       </c>
       <c r="D4" t="n">
-        <v>50.8043001340396</v>
+        <v>8.255698771781436</v>
       </c>
       <c r="E4" t="n">
-        <v>8.410500381452998</v>
+        <v>1.366706311986112</v>
       </c>
       <c r="F4" t="n">
-        <v>9.574595481210123</v>
+        <v>1.555871765696645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
